--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_279_R28.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_279_R28.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6112</v>
+        <v>6.7266</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5051</v>
+        <v>5.5615</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1061</v>
+        <v>1.1651</v>
       </c>
       <c r="G2" t="n">
         <v>2.322</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5058</v>
+        <v>0.6212</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7986</v>
+        <v>-0.145</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7071</v>
+        <v>0.7662</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7887</v>
+        <v>3.3778</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5476</v>
+        <v>2.9015</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2411</v>
+        <v>0.4764</v>
       </c>
       <c r="G3" t="n">
         <v>3.0132</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1523</v>
+        <v>-0.5632</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.3943</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0163</v>
+        <v>1.0671</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4752</v>
+        <v>1.5932</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4589</v>
+        <v>-0.5261</v>
       </c>
       <c r="G4" t="n">
         <v>0.9864000000000001</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.666</v>
+        <v>-0.6152</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1432</v>
+        <v>-0.2104</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8084</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0.5142</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2942</v>
+        <v>0.1598</v>
       </c>
       <c r="G5" t="n">
         <v>0.3673</v>
@@ -844,13 +844,13 @@
         <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2091</v>
+        <v>0.0747</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2838</v>
+        <v>0.1494</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6589</v>
+        <v>0.3551</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0223</v>
+        <v>0.5505</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3634</v>
+        <v>-0.1954</v>
       </c>
       <c r="G6" t="n">
         <v>1.1624</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0532</v>
+        <v>-0.2506</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4129</v>
+        <v>-0.0589</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3598</v>
+        <v>-0.1918</v>
       </c>
       <c r="V6" t="n">
         <v>-0.7886</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1954</v>
+        <v>-0.657</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0323</v>
+        <v>0.2036</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.163</v>
+        <v>-0.8606</v>
       </c>
       <c r="G7" t="n">
         <v>0.0382</v>
@@ -1000,13 +1000,13 @@
         <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4809</v>
+        <v>-0.9425</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5847</v>
+        <v>-0.2822</v>
       </c>
       <c r="V7" t="n">
         <v>-1.6083</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0842</v>
+        <v>-1.7976</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0514</v>
+        <v>-1.6976</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0328</v>
+        <v>-0.1</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7816</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2847</v>
+        <v>0.002</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3049</v>
+        <v>0.2377</v>
       </c>
       <c r="V8" t="n">
         <v>0.1418</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4108</v>
+        <v>-3.1162</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0001</v>
+        <v>-3.2761</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4106</v>
+        <v>0.1599</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.817</v>
+        <v>-4.0173</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5394</v>
+        <v>0.0815</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2776</v>
+        <v>-4.0988</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4845</v>
+        <v>-1.4444</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0847</v>
+        <v>0.1785</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5692</v>
+        <v>-1.6229</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3015</v>
+        <v>-2.5729</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4547</v>
+        <v>-0.097</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8468</v>
+        <v>-2.4759</v>
       </c>
       <c r="P9" t="n">
+        <v>1.3917</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-4.639</v>
-      </c>
       <c r="R9" t="n">
-        <v>3.4793</v>
+        <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4964</v>
+        <v>-0.3488</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7986</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3022</v>
+        <v>0.3231</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9304</v>
+        <v>-0.1418</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2862</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0084</v>
+        <v>-3.7619</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8658</v>
+        <v>-2.8258</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1426</v>
+        <v>-0.9361</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0173</v>
+        <v>-4.8588</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0815</v>
+        <v>-0.1176</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.0988</v>
+        <v>-4.7412</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4444</v>
+        <v>-1.8855</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1785</v>
+        <v>0.3263</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6229</v>
+        <v>-2.2118</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5729</v>
+        <v>-2.9733</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.097</v>
+        <v>-0.4439</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4759</v>
+        <v>-2.5294</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5515</v>
+        <v>3.0154</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.241</v>
+        <v>-0.7587</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2617</v>
+        <v>-0.8527</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0207</v>
+        <v>0.094</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4696</v>
+        <v>-4.1527</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5335</v>
+        <v>-2.9438</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9361</v>
+        <v>-1.209</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.8588</v>
+        <v>-1.817</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1176</v>
+        <v>-1.5394</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.7412</v>
+        <v>-0.2776</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8855</v>
+        <v>0.4845</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3263</v>
+        <v>-1.0847</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.2118</v>
+        <v>1.5692</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9733</v>
+        <v>-2.3015</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4439</v>
+        <v>-0.4547</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.5294</v>
+        <v>-1.8468</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8556</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R11" t="n">
-        <v>3.0154</v>
+        <v>3.4793</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4664</v>
+        <v>-0.2456</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5604</v>
+        <v>-0.145</v>
       </c>
       <c r="U11" t="n">
-        <v>0.094</v>
+        <v>-0.1006</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>1.3558</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.284899999999999</v>
+        <v>-1.2849</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5812999999999988</v>
+        <v>0.5811999999999995</v>
       </c>
       <c r="F12" t="n">
         <v>-1.866</v>
@@ -1357,19 +1357,19 @@
         <v>-3.585199999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>4.578599999999999</v>
+        <v>4.5786</v>
       </c>
       <c r="I12" t="n">
         <v>-8.163699999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>9.351599999999999</v>
+        <v>9.351600000000001</v>
       </c>
       <c r="K12" t="n">
         <v>6.959899999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>2.3918</v>
+        <v>2.391799999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-12.9367</v>
@@ -1384,19 +1384,19 @@
         <v>8.118300000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.278100000000002</v>
+        <v>-9.2781</v>
       </c>
       <c r="R12" t="n">
         <v>17.3966</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.026800000000001</v>
+        <v>-3.0267</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.418</v>
+        <v>-3.4179</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3911000000000002</v>
+        <v>0.3911</v>
       </c>
       <c r="V12" t="n">
         <v>-2.7912</v>
@@ -1405,7 +1405,7 @@
         <v>3.9256</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.716800000000001</v>
+        <v>-6.7168</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.7789</v>
+        <v>7.4073</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1743</v>
+        <v>6.4102</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6046</v>
+        <v>0.9971</v>
       </c>
       <c r="G13" t="n">
         <v>7.5498</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3071</v>
+        <v>0.3213</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.326</v>
+        <v>-0.0901</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0189</v>
+        <v>0.4114</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8414</v>
+        <v>3.1829</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6738</v>
+        <v>2.5929</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1676</v>
+        <v>0.59</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3967</v>
+        <v>0.4042</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8317</v>
+        <v>-1.0479</v>
       </c>
       <c r="I14" t="n">
-        <v>0.435</v>
+        <v>1.4521</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.003</v>
+        <v>1.5518</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7023</v>
+        <v>-0.1646</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6993</v>
+        <v>1.7164</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3937</v>
+        <v>-1.1477</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1294</v>
+        <v>-0.8834</v>
       </c>
       <c r="O14" t="n">
         <v>-0.2643</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8644</v>
+        <v>0.454</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4629</v>
+        <v>-0.1729</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4015</v>
+        <v>0.6269</v>
       </c>
       <c r="V14" t="n">
-        <v>1.214</v>
+        <v>1.8608</v>
       </c>
       <c r="W14" t="n">
         <v>1.214</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2666</v>
+        <v>2.8027</v>
       </c>
       <c r="E15" t="n">
-        <v>2.475</v>
+        <v>1.6122</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7916</v>
+        <v>1.1905</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4042</v>
+        <v>-0.3967</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0479</v>
+        <v>-0.8317</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4521</v>
+        <v>0.435</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5518</v>
+        <v>-0.003</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1646</v>
+        <v>-0.7023</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7164</v>
+        <v>0.6993</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1477</v>
+        <v>-0.3937</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8834</v>
+        <v>-0.1294</v>
       </c>
       <c r="O15" t="n">
         <v>-0.2643</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5377</v>
+        <v>0.8257</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2908</v>
+        <v>0.4013</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8285</v>
+        <v>0.4244</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8608</v>
+        <v>1.214</v>
       </c>
       <c r="W15" t="n">
         <v>1.214</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.4355</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7571</v>
+        <v>0.2496</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8431</v>
+        <v>0.1859</v>
       </c>
       <c r="G16" t="n">
-        <v>0.75</v>
+        <v>0.3756</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0333</v>
+        <v>-0.9962</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7833</v>
+        <v>1.3718</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5976</v>
+        <v>0.4618</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3998</v>
+        <v>-0.7527</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9974</v>
+        <v>1.2146</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8476</v>
+        <v>-0.0862</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6335</v>
+        <v>-0.2435</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.214</v>
+        <v>0.1573</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7098</v>
+        <v>-0.4039</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0351</v>
+        <v>-0.2122</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7449</v>
+        <v>-0.1918</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0316</v>
+        <v>-0.4396</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0137</v>
+        <v>-0.8097</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0179</v>
+        <v>0.3701</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3756</v>
+        <v>-1.1148</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9962</v>
+        <v>0.5114</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3718</v>
+        <v>-1.6262</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4618</v>
+        <v>-1.0181</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7527</v>
+        <v>0.5546</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2146</v>
+        <v>-1.5727</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0862</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2435</v>
+        <v>-0.0431</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>-0.0535</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8079</v>
+        <v>0.4433</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4481</v>
+        <v>0.2084</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3598</v>
+        <v>0.2348</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3209</v>
+        <v>-0.8829</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4558</v>
+        <v>-0.875</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1349</v>
+        <v>-0.0078</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1148</v>
+        <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5114</v>
+        <v>-1.0333</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6262</v>
+        <v>1.7833</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0181</v>
+        <v>1.5976</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5546</v>
+        <v>-0.3998</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5727</v>
+        <v>1.9974</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.8476</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0431</v>
+        <v>-0.6335</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0535</v>
+        <v>-0.214</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5619</v>
+        <v>0.7409</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5623</v>
+        <v>-0.1531</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0004</v>
+        <v>0.894</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8609</v>
+        <v>-0.9655</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1549</v>
+        <v>-0.2721</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0158</v>
+        <v>-0.6934</v>
       </c>
       <c r="G19" t="n">
-        <v>4.1499</v>
+        <v>-0.7336</v>
       </c>
       <c r="H19" t="n">
-        <v>2.042</v>
+        <v>-0.9544</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1079</v>
+        <v>0.2208</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2261</v>
+        <v>-0.1975</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9577</v>
+        <v>-0.7863</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2685</v>
+        <v>0.5889</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0762</v>
+        <v>-0.5361</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9157</v>
+        <v>-0.168</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1605</v>
+        <v>-0.368</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.9432</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0767</v>
+        <v>-0.232</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4955</v>
+        <v>-0.0747</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5812</v>
+        <v>-0.1573</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9655</v>
+        <v>-1.0358</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2721</v>
+        <v>-2.0731</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6934</v>
+        <v>1.0374</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7336</v>
+        <v>0.2401</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9544</v>
+        <v>0.2736</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2208</v>
+        <v>-0.0335</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1975</v>
+        <v>0.4801</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7863</v>
+        <v>0.2996</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5889</v>
+        <v>0.1805</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5361</v>
+        <v>-0.24</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.168</v>
+        <v>-0.026</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.368</v>
+        <v>-0.214</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.232</v>
+        <v>0.6673</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0747</v>
+        <v>-0.0587</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1573</v>
+        <v>0.726</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5462</v>
+        <v>-1.181</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1911</v>
+        <v>-0.8666</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6448</v>
+        <v>-0.3144</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2401</v>
+        <v>-0.9193</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2736</v>
+        <v>-0.4943</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0335</v>
+        <v>-0.425</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4801</v>
+        <v>0.4109</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2996</v>
+        <v>0.6218</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1805</v>
+        <v>-0.2109</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.24</v>
+        <v>-1.3302</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.026</v>
+        <v>-1.1161</v>
       </c>
       <c r="O21" t="n">
         <v>-0.214</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.0154</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1568</v>
+        <v>0.344</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1766</v>
+        <v>-0.1177</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3334</v>
+        <v>0.4617</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9889</v>
+        <v>-1.1977</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3384</v>
+        <v>1.919</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6504</v>
+        <v>-3.1166</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9193</v>
+        <v>4.1499</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4943</v>
+        <v>2.042</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.425</v>
+        <v>2.1079</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4109</v>
+        <v>5.2261</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6218</v>
+        <v>2.9577</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2109</v>
+        <v>2.2685</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3302</v>
+        <v>-1.0762</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1161</v>
+        <v>-0.9157</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.214</v>
+        <v>-0.1605</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R22" t="n">
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4639</v>
+        <v>0.74</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5895</v>
+        <v>0.2596</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1256</v>
+        <v>0.4804</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1418</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.0372</v>
+        <v>-6.0549</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5389</v>
+        <v>-4.9491</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4983</v>
+        <v>-1.1058</v>
       </c>
       <c r="G23" t="n">
         <v>-6.7202</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0697</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9709</v>
+        <v>-0.3811</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0988</v>
+        <v>0.2937</v>
       </c>
       <c r="V23" t="n">
         <v>2.1444</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.284899999999999</v>
+        <v>2.071</v>
       </c>
       <c r="E24" t="n">
-        <v>2.938299999999998</v>
+        <v>2.938300000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6534</v>
+        <v>-0.867</v>
       </c>
       <c r="G24" t="n">
-        <v>3.584999999999999</v>
+        <v>3.585000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-4.5784</v>
@@ -2311,7 +2311,7 @@
         <v>-9.351500000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.9597</v>
+        <v>-6.959700000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-2.3915</v>
@@ -2323,16 +2323,16 @@
         <v>-17.3963</v>
       </c>
       <c r="R24" t="n">
-        <v>9.278299999999998</v>
+        <v>9.2783</v>
       </c>
       <c r="S24" t="n">
-        <v>3.0267</v>
+        <v>3.8132</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.391</v>
+        <v>-0.3912</v>
       </c>
       <c r="U24" t="n">
-        <v>3.4177</v>
+        <v>4.2042</v>
       </c>
       <c r="V24" t="n">
         <v>2.7912</v>
